--- a/DP700_SkillsMeasured.xlsx
+++ b/DP700_SkillsMeasured.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sh_na\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marina\Desktop\Miladin\DataScience\Microsoft\Fabric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B9BF677-D85E-4A51-A1AB-F72B829CF38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A61CA7-4C75-4BF4-A264-01EFF0D801CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="423" xr2:uid="{197F7256-46D1-4BCD-8146-4714AB14894A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="423" xr2:uid="{197F7256-46D1-4BCD-8146-4714AB14894A}"/>
   </bookViews>
   <sheets>
     <sheet name="DP-700 Study Guide Tracker" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Learning Path" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DP-700 Study Guide Tracker'!$A$1:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DP-700 Study Guide Tracker'!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="93">
   <si>
     <t>Design and implement loading patterns</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Choose an appropriate data store</t>
   </si>
   <si>
-    <t>Choose between dataflows, notebooks, and T-SQL for data transformation</t>
-  </si>
-  <si>
     <t>Create and manage shortcuts to data</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>Ingest data by using pipelines</t>
   </si>
   <si>
-    <t>Transform data by using PySpark, SQL, and KQL</t>
-  </si>
-  <si>
     <t>Denormalize data</t>
   </si>
   <si>
@@ -196,9 +190,6 @@
     <t>Implement item-level access controls</t>
   </si>
   <si>
-    <t>Implement row-level, column-level, object-level, and file-level access controls</t>
-  </si>
-  <si>
     <t>Implement dynamic data masking</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>Orchestrate processes</t>
   </si>
   <si>
-    <t>Choose between a pipeline and a notebook</t>
-  </si>
-  <si>
     <t>Design and implement schedules and event-based triggers</t>
   </si>
   <si>
@@ -296,6 +284,42 @@
   </si>
   <si>
     <t>Learning Path URL</t>
+  </si>
+  <si>
+    <t>Configure Spark workspace settings</t>
+  </si>
+  <si>
+    <t>Implement row-level, column-level, object-level, and folder/file-level access controls</t>
+  </si>
+  <si>
+    <t>Implement and use workspace logging</t>
+  </si>
+  <si>
+    <t>Configure and implement OneLake security</t>
+  </si>
+  <si>
+    <t>Choose between Dataflow Gen 2, a pipeline and a notebook</t>
+  </si>
+  <si>
+    <t>Choose between dataflows, notebooks, KQL and T-SQL for data transformation</t>
+  </si>
+  <si>
+    <t>Ingest data by using continuous integration from OneLake</t>
+  </si>
+  <si>
+    <t>Transform data by using Power Query (M), PySpark, SQL, and KQL</t>
+  </si>
+  <si>
+    <t>Choose between native storage, mirrored storage, or shortcuts in Real-Time Intelligence</t>
+  </si>
+  <si>
+    <t>Choose between accelerated shortcuts and non-accelerated shortcuts in Real-Time Intelligence</t>
+  </si>
+  <si>
+    <t>Identify and resolve Shortcut errors</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -800,624 +824,630 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00E6A71-0576-4B77-AEC1-148D053D2DA4}">
-  <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="4" max="4" width="38.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" customWidth="1"/>
-    <col min="6" max="6" width="68.90625" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" customWidth="1"/>
-    <col min="8" max="8" width="14.90625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="26.08984375" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="6" width="68.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="12" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="12" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>62</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
       </c>
       <c r="C2">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
       </c>
-      <c r="E7">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8">
         <v>6</v>
       </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8">
-        <v>7</v>
-      </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>48</v>
       </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14">
         <v>12</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14">
-        <v>13</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16">
-        <v>15</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20">
         <v>21</v>
       </c>
-      <c r="D17" t="s">
-        <v>0</v>
-      </c>
-      <c r="E17">
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>16</v>
       </c>
-      <c r="F17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18">
+      <c r="F20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21">
         <v>21</v>
       </c>
-      <c r="D18" t="s">
-        <v>0</v>
-      </c>
-      <c r="E18">
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>17</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19">
+      <c r="F21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22">
         <v>21</v>
       </c>
-      <c r="D19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19">
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>18</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21">
-        <v>20</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22">
-        <v>21</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
-        <v>2</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="7">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23">
         <v>22</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24">
         <v>22</v>
@@ -1426,24 +1456,24 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>23</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>22</v>
@@ -1452,50 +1482,50 @@
         <v>4</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>2</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>2</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="7">
         <v>22</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <v>22</v>
@@ -1504,24 +1534,24 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4">
         <v>12</v>
       </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C28">
         <v>22</v>
@@ -1530,567 +1560,761 @@
         <v>4</v>
       </c>
       <c r="E28">
+        <v>23</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4">
+        <v>12</v>
+      </c>
+      <c r="I28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>24</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>26</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32">
         <v>27</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28">
-        <v>0.5</v>
-      </c>
-      <c r="H28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>2</v>
-      </c>
-      <c r="B29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29">
-        <v>23</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29">
-        <v>28</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30">
-        <v>23</v>
-      </c>
-      <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30">
-        <v>29</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31">
-        <v>23</v>
-      </c>
-      <c r="D31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31">
-        <v>30</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>2</v>
-      </c>
-      <c r="B32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32">
-        <v>23</v>
-      </c>
-      <c r="D32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32">
-        <v>31</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>18</v>
+      <c r="F32" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>23</v>
       </c>
       <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33">
+        <v>28</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>28</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4">
+        <v>2</v>
+      </c>
+      <c r="I34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>28</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>29</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E33">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>30</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>31</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39">
         <v>32</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>3</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34">
-        <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>3</v>
-      </c>
-      <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35">
-        <v>31</v>
-      </c>
-      <c r="D35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35">
-        <v>34</v>
-      </c>
-      <c r="F35" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>3</v>
-      </c>
-      <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36">
-        <v>31</v>
-      </c>
-      <c r="D36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36">
-        <v>35</v>
-      </c>
-      <c r="F36" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>3</v>
-      </c>
-      <c r="B37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37">
-        <v>31</v>
-      </c>
-      <c r="D37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37">
-        <v>36</v>
-      </c>
-      <c r="F37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38">
-        <v>32</v>
-      </c>
-      <c r="D38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38">
-        <v>37</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>3</v>
-      </c>
-      <c r="B39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39">
-        <v>38</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>27</v>
+      <c r="F39" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C40">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E40">
-        <v>39</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="F40" t="s">
+        <v>19</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E41">
-        <v>40</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E42">
-        <v>41</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E43">
-        <v>42</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F43" t="s">
+        <v>22</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E44">
-        <v>43</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E45">
-        <v>44</v>
-      </c>
-      <c r="F45" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>3</v>
       </c>
       <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46">
         <v>39</v>
       </c>
-      <c r="C46">
-        <v>33</v>
-      </c>
-      <c r="D46" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46">
-        <v>45</v>
-      </c>
-      <c r="F46" t="s">
-        <v>35</v>
+      <c r="F46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E47">
-        <v>46</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E48">
-        <v>47</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C49">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49">
+        <v>42</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50">
+        <v>42</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <v>0</v>
+      </c>
+      <c r="I50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51">
         <v>33</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51">
+        <v>43</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52">
+        <v>33</v>
+      </c>
+      <c r="D52" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52">
+        <v>44</v>
+      </c>
+      <c r="F52" t="s">
         <v>32</v>
       </c>
-      <c r="E49">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53">
+        <v>33</v>
+      </c>
+      <c r="D53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53">
+        <v>45</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54">
+        <v>46</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55">
+        <v>47</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56">
+        <v>33</v>
+      </c>
+      <c r="D56" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56">
         <v>48</v>
       </c>
-      <c r="F49" t="s">
-        <v>38</v>
-      </c>
-      <c r="G49">
-        <v>0.25</v>
-      </c>
-      <c r="H49" s="4">
+      <c r="F56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H49" xr:uid="{C00E6A71-0576-4B77-AEC1-148D053D2DA4}"/>
-  <conditionalFormatting sqref="F2:F49">
+  <autoFilter ref="A1:H56" xr:uid="{C00E6A71-0576-4B77-AEC1-148D053D2DA4}"/>
+  <conditionalFormatting sqref="F2:F56">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND($G2&gt;0, $G2&lt;1)</formula>
     </cfRule>
@@ -2109,21 +2333,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E36F6C-F530-445B-8B96-71263B387932}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2131,7 +2355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2139,7 +2363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2147,7 +2371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2155,7 +2379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2163,7 +2387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -2171,7 +2395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>12</v>
       </c>
@@ -2179,7 +2403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12</v>
       </c>
@@ -2187,7 +2411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123</v>
       </c>
@@ -2195,7 +2419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>123</v>
       </c>
@@ -2203,7 +2427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>123</v>
       </c>
@@ -2222,88 +2446,88 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351084D2-7CF8-432B-B66B-4E53B6E9F1DC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="49.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="84.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
       <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
